--- a/NineReincarnation/Assets/08. Scripts/Data/DialogueData.xlsx
+++ b/NineReincarnation/Assets/08. Scripts/Data/DialogueData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kdsh6\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\권동현\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79979814-795D-43E1-AFD5-D813427BAEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910A83B8-6466-498F-A019-39CC7E7DA891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="설명" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="75">
   <si>
     <t>[함수 설명]</t>
   </si>
@@ -180,67 +180,22 @@
     <t>EventType</t>
   </si>
   <si>
+    <t>IsAuto</t>
+  </si>
+  <si>
+    <t>Duration</t>
+  </si>
+  <si>
     <t>NextID</t>
   </si>
   <si>
-    <t>Scripts</t>
+    <t>비고</t>
   </si>
   <si>
     <t>{fade a=3.5} 으으... 머리야...</t>
   </si>
   <si>
     <t>{fade a=3.5} 난 분명 교실에 있었던 것 같은데 여기는 도대체 어디지?</t>
-  </si>
-  <si>
-    <t>{fade a=3.5} 왠지 모르게 으스스한 기분이 드네</t>
-  </si>
-  <si>
-    <t>{fade a=3.5} 그래도 뭐, 호랑이 굴에 들어가도 정신만 바짝 차리면 빠져나올 수 있다 했잖아!</t>
-  </si>
-  <si>
-    <t>Bubble, Camera</t>
-  </si>
-  <si>
-    <t>{fade a=3.5}&lt;bounce a=0.2&gt;일단 가보자고!&lt;/&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{fade a=3.5}어떻게든 나갈 방법을 찾아서... </t>
-  </si>
-  <si>
-    <t>{horiexp}&lt;size=120%&gt;난 반드시 집으로 돌아갈 거야!!!</t>
-  </si>
-  <si>
-    <t>줌아웃</t>
-  </si>
-  <si>
-    <t>{fade a=3.5} 근데 어디로 가야하지?</t>
-  </si>
-  <si>
-    <t>가위 날아감</t>
-  </si>
-  <si>
-    <t>{fade a=3.5} 저건... 아까 내가 교실에서 봤던 그 가위잖아!!</t>
-  </si>
-  <si>
-    <t>{fade a=3.5} &lt;wiggle a=0.1&gt;거기 서!!!&lt;/&gt;</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>ImageName</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>안나</t>
-  </si>
-  <si>
-    <t>Anna_Confusion</t>
-  </si>
-  <si>
-    <t>Anna_Blank</t>
   </si>
   <si>
     <r>
@@ -264,7 +219,28 @@
     </r>
   </si>
   <si>
-    <t>Anna_Smile</t>
+    <t>{fade a=3.5} 왠지 모르게 으스스한 기분이 드네</t>
+  </si>
+  <si>
+    <t>{fade a=3.5} 그래도 뭐, 호랑이 굴에 들어가도 정신만 바짝 차리면 빠져나올 수 있다 했잖아!</t>
+  </si>
+  <si>
+    <t>Bubble, Camera</t>
+  </si>
+  <si>
+    <t>{fade a=3.5}&lt;bounce a=0.2&gt;일단 가보자고!&lt;/&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{fade a=3.5}어떻게든 나갈 방법을 찾아서... </t>
+  </si>
+  <si>
+    <t>{horiexp}&lt;size=120%&gt;난 반드시 집으로 돌아갈 거야!!!</t>
+  </si>
+  <si>
+    <t>줌아웃</t>
+  </si>
+  <si>
+    <t>{fade a=3.5} 근데 어디로 가야하지?</t>
   </si>
   <si>
     <r>
@@ -288,6 +264,33 @@
     </r>
   </si>
   <si>
+    <t>{fade a=3.5} 저건... 아까 내가 교실에서 봤던 그 가위잖아!!</t>
+  </si>
+  <si>
+    <t>{fade a=3.5} &lt;wiggle a=0.1&gt;거기 서!!!&lt;/&gt;</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>ImageName</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>안나</t>
+  </si>
+  <si>
+    <t>Anna_Confusion</t>
+  </si>
+  <si>
+    <t>Anna_Blank</t>
+  </si>
+  <si>
+    <t>Anna_Smile</t>
+  </si>
+  <si>
     <t>Anna_Determination</t>
   </si>
   <si>
@@ -295,9 +298,6 @@
   </si>
   <si>
     <t>Size</t>
-  </si>
-  <si>
-    <t>Duration</t>
   </si>
   <si>
     <t>ZoomIn</t>
@@ -565,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -649,6 +649,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -868,15 +871,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A2:G12"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="32.140625" customWidth="1"/>
+    <col min="2" max="2" width="32.109375" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="37" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" customWidth="1"/>
+    <col min="7" max="7" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1042,18 +1046,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="61.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="61.28515625" customWidth="1"/>
-    <col min="7" max="7" width="37" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="67.21875" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="61.21875" customWidth="1"/>
+    <col min="9" max="9" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="20" t="s">
         <v>38</v>
       </c>
@@ -1066,224 +1071,328 @@
       <c r="D1" s="20" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="21">
         <v>101001</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="35">
+        <v>0</v>
+      </c>
+      <c r="E2" s="21">
         <v>101002</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:6">
       <c r="A3" s="21">
         <v>101002</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" s="21">
+        <v>0</v>
+      </c>
+      <c r="E3" s="21">
         <v>101003</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:6">
       <c r="A4" s="21">
         <v>101003</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="35">
+        <v>0</v>
+      </c>
+      <c r="E4" s="21">
         <v>101004</v>
       </c>
-      <c r="D4" s="23" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="F4" s="23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="21">
         <v>101004</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="21">
+        <v>0</v>
+      </c>
+      <c r="E5" s="21">
         <v>101005</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="F5" s="23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="21">
         <v>101005</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="35">
+        <v>0</v>
+      </c>
+      <c r="E6" s="21">
         <v>101006</v>
       </c>
-      <c r="D6" s="23"/>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="F6" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="21">
         <v>101006</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="21">
+        <v>0</v>
+      </c>
+      <c r="E7" s="21">
         <v>101007</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="F7" s="23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="21">
         <v>101007</v>
       </c>
       <c r="B8" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="35">
+        <v>0</v>
+      </c>
+      <c r="E8" s="21">
         <v>101008</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="F8" s="23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="21">
         <v>101008</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="21">
+        <v>49</v>
+      </c>
+      <c r="C9" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" s="21">
+        <v>0</v>
+      </c>
+      <c r="E9" s="21">
         <v>101009</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="F9" s="23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="21">
         <v>101009</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="21">
+        <v>49</v>
+      </c>
+      <c r="C10" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" s="35">
+        <v>0</v>
+      </c>
+      <c r="E10" s="21">
         <v>101010</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="F10" s="23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="21">
         <v>101010</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="21">
+        <v>49</v>
+      </c>
+      <c r="C11" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="21">
+        <v>0</v>
+      </c>
+      <c r="E11" s="21">
         <v>101011</v>
       </c>
-      <c r="D11" s="23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="F11" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="21">
         <v>101011</v>
       </c>
       <c r="B12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="35">
+        <v>0</v>
+      </c>
+      <c r="E12" s="21">
         <v>101012</v>
       </c>
-      <c r="D12" s="23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="F12" s="23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="21">
         <v>101012</v>
       </c>
       <c r="B13" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="21">
+        <v>0</v>
+      </c>
+      <c r="E13" s="21">
         <v>101013</v>
       </c>
-      <c r="D13" s="23" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="F13" s="23" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="21">
         <v>101013</v>
       </c>
       <c r="B14" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="35">
+        <v>0</v>
+      </c>
+      <c r="E14" s="21">
         <v>101014</v>
       </c>
-      <c r="D14" s="23" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="F14" s="22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="21">
         <v>101014</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="21">
+        <v>0</v>
+      </c>
+      <c r="E15" s="21">
         <v>101015</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="F15" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="21">
         <v>101015</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="35">
+        <v>0</v>
+      </c>
+      <c r="E16" s="21">
         <v>101016</v>
       </c>
-      <c r="D16" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="F16" s="23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="21">
         <v>101016</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" s="21">
+        <v>0</v>
+      </c>
+      <c r="E17" s="21">
         <v>101017</v>
       </c>
-      <c r="D17" s="23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="F17" s="23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="21">
         <v>101017</v>
       </c>
@@ -1291,13 +1400,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:6">
       <c r="A19" s="21"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:6">
       <c r="A22" s="22"/>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:6">
       <c r="A23" s="22"/>
     </row>
   </sheetData>
@@ -1312,11 +1421,11 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="4" width="61.28515625" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1"/>
+    <col min="4" max="4" width="61.21875" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1324,16 +1433,16 @@
         <v>38</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D1" s="24" t="s">
         <v>32</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1341,13 +1450,13 @@
         <v>101003</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1355,96 +1464,84 @@
         <v>101004</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="21">
-        <v>101005</v>
+        <v>101006</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="22" t="s">
         <v>61</v>
       </c>
+      <c r="C4" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="22"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="21">
-        <v>101006</v>
+        <v>101007</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="21">
-        <v>101007</v>
+        <v>101012</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="21">
-        <v>101012</v>
+        <v>101014</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="21">
-        <v>101013</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>58</v>
-      </c>
+      <c r="A8" s="21"/>
+      <c r="B8" s="23"/>
       <c r="C8" s="25"/>
       <c r="D8" s="23"/>
-      <c r="E8" s="22" t="s">
-        <v>63</v>
-      </c>
+      <c r="E8" s="22"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="21">
-        <v>101014</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>53</v>
-      </c>
+      <c r="A9" s="21"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="17" type="noConversion"/>
@@ -1458,10 +1555,10 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.140625" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" customWidth="1"/>
+    <col min="5" max="5" width="25.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1469,16 +1566,16 @@
         <v>38</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1" s="26" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1566,10 +1663,10 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1577,27 +1674,22 @@
         <v>38</v>
       </c>
       <c r="B1" s="31" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="31" t="s">
-        <v>67</v>
-      </c>
+      <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="21">
         <v>101001</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>73</v>
-      </c>
-      <c r="D2" s="22">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1605,13 +1697,10 @@
         <v>101002</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>74</v>
-      </c>
-      <c r="D3" s="22">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1625,65 +1714,73 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="3" max="3" width="38.28515625" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" customWidth="1"/>
+    <col min="4" max="4" width="39.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="32" t="s">
         <v>38</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C1" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="32" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="21">
         <v>101008</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>61</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="21">
         <v>101009</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>61</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="21">
         <v>101010</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>61</v>
+      </c>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="21">
         <v>101015</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>54</v>
+        <v>61</v>
+      </c>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/NineReincarnation/Assets/08. Scripts/Data/DialogueData.xlsx
+++ b/NineReincarnation/Assets/08. Scripts/Data/DialogueData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\권동현\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Nine-Reincarnation\NineReincarnation\Assets\08. Scripts\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910A83B8-6466-498F-A019-39CC7E7DA891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAA613B-F2D5-4E1C-A3B5-BE371A271EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="348" yWindow="1320" windowWidth="21396" windowHeight="10884" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="설명" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="84">
   <si>
     <t>[함수 설명]</t>
   </si>
@@ -174,15 +174,15 @@
     <t>0b100000</t>
   </si>
   <si>
+    <t>카메라 기준 크기</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
     <t>EventType</t>
   </si>
   <si>
-    <t>IsAuto</t>
-  </si>
-  <si>
     <t>Duration</t>
   </si>
   <si>
@@ -196,27 +196,6 @@
   </si>
   <si>
     <t>{fade a=3.5} 난 분명 교실에 있었던 것 같은데 여기는 도대체 어디지?</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">[이벤트] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>좌우 한 번씩 2초간 보기</t>
-    </r>
   </si>
   <si>
     <t>{fade a=3.5} 왠지 모르게 으스스한 기분이 드네</t>
@@ -320,12 +299,52 @@
   <si>
     <t>Anna_Wake</t>
   </si>
+  <si>
+    <t>Anna</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShowName</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Direction</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Anna_LookAround</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Right</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Left</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Round</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spiky</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -448,6 +467,27 @@
       <name val="Arial"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -565,7 +605,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -616,13 +656,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -647,11 +687,20 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -870,7 +919,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A2:G12"/>
+  <dimension ref="A2:G13"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="32.109375" customWidth="1"/>
@@ -899,11 +948,11 @@
       <c r="C3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="8" t="s">
@@ -1031,6 +1080,14 @@
     </row>
     <row r="12" spans="1:7">
       <c r="G12" s="17"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="E13" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="20">
+        <v>8.4375</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1046,368 +1103,348 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.21875" customWidth="1"/>
-    <col min="2" max="2" width="18.21875" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" customWidth="1"/>
+    <col min="3" max="3" width="19.77734375" customWidth="1"/>
+    <col min="4" max="4" width="27.77734375" customWidth="1"/>
+    <col min="5" max="5" width="84.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="67.21875" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="61.21875" customWidth="1"/>
     <col min="9" max="9" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="20" t="s">
+    <row r="1" spans="1:6" ht="13.2">
+      <c r="A1" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="B1" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="C1" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="D1" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="E1" s="21" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="21">
+      <c r="F1" s="21"/>
+    </row>
+    <row r="2" spans="1:6" ht="13.2">
+      <c r="A2" s="22">
         <v>101001</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" s="35">
+      <c r="C2" s="22">
         <v>0</v>
       </c>
-      <c r="E2" s="21">
+      <c r="D2" s="22">
         <v>101002</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="21">
+    <row r="3" spans="1:6" ht="13.2">
+      <c r="A3" s="22">
         <v>101002</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" s="21">
+      <c r="C3" s="22">
         <v>0</v>
       </c>
-      <c r="E3" s="21">
+      <c r="D3" s="22">
         <v>101003</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="21">
+    <row r="4" spans="1:6" ht="13.2">
+      <c r="A4" s="22">
         <v>101003</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="21" t="b">
+      <c r="C4" s="22">
         <v>0</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="22">
+        <v>101004</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="23"/>
+    </row>
+    <row r="5" spans="1:6" ht="13.2">
+      <c r="A5" s="22">
+        <v>101004</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="22">
         <v>0</v>
       </c>
-      <c r="E4" s="21">
-        <v>101004</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="21">
-        <v>101004</v>
-      </c>
-      <c r="B5" s="22" t="s">
+      <c r="D5" s="22">
+        <v>101005</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="23"/>
+    </row>
+    <row r="6" spans="1:6" ht="13.2">
+      <c r="A6" s="22">
+        <v>101005</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="22">
+        <v>0</v>
+      </c>
+      <c r="D6" s="22">
+        <v>101006</v>
+      </c>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+    </row>
+    <row r="7" spans="1:6" ht="13.2">
+      <c r="A7" s="22">
+        <v>101006</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="22">
+        <v>0</v>
+      </c>
+      <c r="D7" s="22">
+        <v>101007</v>
+      </c>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+    </row>
+    <row r="8" spans="1:6" ht="13.2">
+      <c r="A8" s="22">
+        <v>101007</v>
+      </c>
+      <c r="B8" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="21" t="b">
+      <c r="C8" s="22">
         <v>0</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D8" s="22">
+        <v>101008</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="23"/>
+    </row>
+    <row r="9" spans="1:6" ht="13.2">
+      <c r="A9" s="22">
+        <v>101008</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="22">
         <v>0</v>
       </c>
-      <c r="E5" s="21">
-        <v>101005</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="21">
-        <v>101005</v>
-      </c>
-      <c r="B6" s="22" t="s">
+      <c r="D9" s="22">
+        <v>101009</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="23"/>
+    </row>
+    <row r="10" spans="1:6" ht="13.2">
+      <c r="A10" s="22">
+        <v>101009</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="22">
+        <v>0</v>
+      </c>
+      <c r="D10" s="22">
+        <v>101010</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="23"/>
+    </row>
+    <row r="11" spans="1:6" ht="13.2">
+      <c r="A11" s="22">
+        <v>101010</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="22">
+        <v>0</v>
+      </c>
+      <c r="D11" s="22">
+        <v>101011</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="23"/>
+    </row>
+    <row r="12" spans="1:6" ht="13.2">
+      <c r="A12" s="22">
+        <v>101011</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="22">
+        <v>2</v>
+      </c>
+      <c r="D12" s="22">
+        <v>101012</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="23"/>
+    </row>
+    <row r="13" spans="1:6" ht="13.2">
+      <c r="A13" s="22">
+        <v>101012</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="22">
+        <v>2</v>
+      </c>
+      <c r="D13" s="22">
+        <v>101013</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="23"/>
+    </row>
+    <row r="14" spans="1:6" ht="13.2">
+      <c r="A14" s="22">
+        <v>101013</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="22">
+        <v>0</v>
+      </c>
+      <c r="D14" s="22">
+        <v>101014</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="23"/>
+    </row>
+    <row r="15" spans="1:6" ht="13.2">
+      <c r="A15" s="22">
+        <v>101014</v>
+      </c>
+      <c r="B15" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="D6" s="35">
+      <c r="C15" s="22">
         <v>0</v>
       </c>
-      <c r="E6" s="21">
-        <v>101006</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="21">
-        <v>101006</v>
-      </c>
-      <c r="B7" s="22" t="s">
+      <c r="D15" s="22">
+        <v>101015</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="20"/>
+    </row>
+    <row r="16" spans="1:6" ht="13.2">
+      <c r="A16" s="22">
+        <v>101015</v>
+      </c>
+      <c r="B16" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="21" t="b">
+      <c r="C16" s="22">
         <v>0</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D16" s="22">
+        <v>101016</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="23"/>
+    </row>
+    <row r="17" spans="1:6" ht="13.2">
+      <c r="A17" s="22">
+        <v>101016</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="22">
         <v>0</v>
       </c>
-      <c r="E7" s="21">
-        <v>101007</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="21">
-        <v>101007</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="21" t="b">
+      <c r="D17" s="22">
+        <v>101017</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="23"/>
+    </row>
+    <row r="18" spans="1:6" ht="13.2">
+      <c r="A18" s="22">
+        <v>101017</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="22">
         <v>0</v>
       </c>
-      <c r="D8" s="35">
-        <v>0</v>
-      </c>
-      <c r="E8" s="21">
-        <v>101008</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="21">
-        <v>101008</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="D9" s="21">
-        <v>0</v>
-      </c>
-      <c r="E9" s="21">
-        <v>101009</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="21">
-        <v>101009</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="D10" s="35">
-        <v>0</v>
-      </c>
-      <c r="E10" s="21">
-        <v>101010</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="21">
-        <v>101010</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="21">
-        <v>0</v>
-      </c>
-      <c r="E11" s="21">
-        <v>101011</v>
-      </c>
-      <c r="F11" s="23" t="s">
+      <c r="D18" s="22">
+        <v>101018</v>
+      </c>
+      <c r="E18" s="23" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="21">
-        <v>101011</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="D12" s="35">
-        <v>0</v>
-      </c>
-      <c r="E12" s="21">
-        <v>101012</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="21">
-        <v>101012</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="21">
-        <v>0</v>
-      </c>
-      <c r="E13" s="21">
-        <v>101013</v>
-      </c>
-      <c r="F13" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="21">
-        <v>101013</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="D14" s="35">
-        <v>0</v>
-      </c>
-      <c r="E14" s="21">
-        <v>101014</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="21">
-        <v>101014</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" s="21">
-        <v>0</v>
-      </c>
-      <c r="E15" s="21">
-        <v>101015</v>
-      </c>
-      <c r="F15" s="23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="21">
-        <v>101015</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" s="35">
-        <v>0</v>
-      </c>
-      <c r="E16" s="21">
-        <v>101016</v>
-      </c>
-      <c r="F16" s="23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="21">
-        <v>101016</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="D17" s="21">
-        <v>0</v>
-      </c>
-      <c r="E17" s="21">
-        <v>101017</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="21">
-        <v>101017</v>
-      </c>
-      <c r="B18" s="22" t="s">
+      <c r="F18" s="23"/>
+    </row>
+    <row r="19" spans="1:6" ht="13.2">
+      <c r="A19" s="22">
+        <v>101018</v>
+      </c>
+      <c r="B19" s="20" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="21"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="22"/>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="22"/>
+    <row r="20" spans="1:6" ht="13.2">
+      <c r="A20" s="22"/>
+    </row>
+    <row r="23" spans="1:6" ht="13.2">
+      <c r="A23" s="20"/>
+    </row>
+    <row r="24" spans="1:6" ht="13.2">
+      <c r="A24" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="17" type="noConversion"/>
@@ -1430,115 +1467,108 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="24" t="s">
         <v>58</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>59</v>
       </c>
       <c r="D1" s="24" t="s">
         <v>32</v>
       </c>
       <c r="E1" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="22">
+        <v>101003</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="21">
-        <v>101003</v>
-      </c>
-      <c r="B2" s="23" t="s">
+      <c r="C2" s="25" t="s">
         <v>61</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>62</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="21">
+      <c r="A3" s="22">
         <v>101004</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="21">
-        <v>101006</v>
+      <c r="A4" s="22">
+        <v>101007</v>
       </c>
       <c r="B4" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="D4" s="23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="22">
+        <v>101008</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="22">
+        <v>101013</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="22"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="21">
-        <v>101007</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="25" t="s">
+      <c r="D6" s="23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="22">
+        <v>101015</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="21">
-        <v>101012</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="21">
-        <v>101014</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>65</v>
-      </c>
       <c r="D7" s="23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="21"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="22"/>
-    </row>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5"/>
     <row r="9" spans="1:5">
-      <c r="A9" s="21"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="23"/>
       <c r="C9" s="25"/>
       <c r="D9" s="23"/>
@@ -1563,13 +1593,13 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="26" t="s">
         <v>66</v>
-      </c>
-      <c r="C1" s="26" t="s">
-        <v>67</v>
       </c>
       <c r="D1" s="26" t="s">
         <v>41</v>
@@ -1579,75 +1609,75 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="21">
-        <v>101008</v>
+      <c r="A2" s="22">
+        <v>101009</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" s="29">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="29">
         <v>0.8</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="21">
-        <v>101009</v>
+      <c r="A3" s="22">
+        <v>101010</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C3" s="29">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="D3" s="29">
         <v>0.8</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="21">
-        <v>101010</v>
+      <c r="A4" s="22">
+        <v>101011</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="29">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="D4" s="29">
         <v>-1</v>
       </c>
-      <c r="E4" s="22" t="s">
-        <v>70</v>
+      <c r="E4" s="20" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="30">
-        <v>101011</v>
+        <v>101012</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="21">
-        <v>4</v>
-      </c>
-      <c r="D5" s="21">
+        <v>70</v>
+      </c>
+      <c r="C5" s="22">
+        <v>7</v>
+      </c>
+      <c r="D5" s="22">
         <v>0.8</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="30">
-        <v>101016</v>
+        <v>101017</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="21">
-        <v>4</v>
-      </c>
-      <c r="D6" s="21">
+        <v>70</v>
+      </c>
+      <c r="C6" s="22">
+        <v>8</v>
+      </c>
+      <c r="D6" s="22">
         <v>0.8</v>
       </c>
     </row>
@@ -1662,45 +1692,81 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="13.2">
       <c r="A1" s="31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" s="31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="13.2">
+      <c r="A2" s="22">
+        <v>101001</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="31"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="21">
-        <v>101001</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" s="22" t="s">
+      <c r="D2" s="36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="13.2">
+      <c r="A3" s="22">
+        <v>101002</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="20" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="21">
-        <v>101002</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="22" t="s">
+      <c r="D3" s="36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A4" s="22">
+        <v>101005</v>
+      </c>
+      <c r="B4" s="36" t="s">
         <v>74</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A5" s="22">
+        <v>101006</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1723,64 +1789,72 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="32" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>83</v>
       </c>
       <c r="D1" s="32" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="21">
-        <v>101008</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" s="23"/>
+      <c r="A2" s="22">
+        <v>101009</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>80</v>
+      </c>
       <c r="D2" s="23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="22">
+        <v>101010</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="23" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="21">
-        <v>101009</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" s="22">
+        <v>101011</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="23" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="21">
-        <v>101010</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23" t="s">
-        <v>52</v>
-      </c>
-    </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="21">
-        <v>101015</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="23"/>
+      <c r="A5" s="22">
+        <v>101016</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>80</v>
+      </c>
       <c r="D5" s="23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
